--- a/experiment-1/oo_mvc_type.xlsx
+++ b/experiment-1/oo_mvc_type.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maik Bieleke\My Drive\Labor\psychopy-apparatus\experiments\experiment-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maik Bieleke\My Drive\Labor\dfg-dynamind\experiment-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07321BCC-3359-4FC1-8A35-FAFB0D2072EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F71D81-A322-4A9B-9AA0-B8660CFF2E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{3C72E597-D4FB-469B-AEF7-42009E7D3B97}"/>
+    <workbookView xWindow="36756" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3C72E597-D4FB-469B-AEF7-42009E7D3B97}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,19 +38,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>practice</t>
+    <t>maxforce_type</t>
   </si>
   <si>
-    <t>cond_maxforce_duration</t>
+    <t>maxforce_duration</t>
   </si>
   <si>
-    <t>cond_maxforce_type</t>
+    <t>maxforce_repetitions</t>
   </si>
   <si>
-    <t>cond_num_maxforce</t>
+    <t>Practice</t>
   </si>
   <si>
-    <t>calibration</t>
+    <t>Calibration</t>
   </si>
 </sst>
 </file>
@@ -425,17 +425,17 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -443,13 +443,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="C2">
-        <v>450</v>
+        <v>999</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
